--- a/02_加值成品/歷屆試題/109年會考自然科.xlsx
+++ b/02_加值成品/歷屆試題/109年會考自然科.xlsx
@@ -1026,7 +1026,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>輪軸屬於槓桿原理的變形，力矩＝力×半徑。要省力就必須在「半徑較大的輪」上施力，並將重物懸掛於「半徑較小的軸」上，如此施力可小於重物重量；反之則會費力。</t>
+          <t>輪軸是槓桿原理的應用：施力臂(輪的半徑)越長，就越省力。要省力就必須在「半徑較大的輪」上施力，並將重物懸掛於「半徑較小的軸」上，如此施力可小於重物重量；反之則會費力。</t>
         </is>
       </c>
     </row>
